--- a/qqq_tqqq_return.xlsx
+++ b/qqq_tqqq_return.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11550" windowHeight="5150"/>
+    <workbookView windowWidth="19200" windowHeight="6800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -59,6 +59,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -526,154 +533,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1030,7 +1037,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="13.6363636363636" customWidth="1"/>
-    <col min="2" max="3" width="12.8181818181818" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3636363636364" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1818181818182" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1049,10 +1057,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>0.172725464013983</v>
+        <v>0.173243913620921</v>
       </c>
       <c r="C2" s="1">
-        <v>0.438057065078531</v>
+        <v>0.437300996285237</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1060,10 +1068,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>0.312276012629918</v>
+        <v>0.313928805596892</v>
       </c>
       <c r="C3" s="1">
-        <v>0.797561756343892</v>
+        <v>0.804188995686226</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1071,10 +1079,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>0.51889597120594</v>
+        <v>0.521151357013074</v>
       </c>
       <c r="C4" s="1">
-        <v>1.51658129584604</v>
+        <v>1.53201381129289</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1082,10 +1090,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>1.03148385529191</v>
+        <v>1.02897172892981</v>
       </c>
       <c r="C5" s="1">
-        <v>3.28179609241294</v>
+        <v>3.24687018228803</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1093,10 +1101,10 @@
         <v>10</v>
       </c>
       <c r="B6" s="1">
-        <v>2.69324169105462</v>
+        <v>2.71529145991317</v>
       </c>
       <c r="C6" s="1">
-        <v>4.83020106621927</v>
+        <v>4.91195542449738</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1104,10 +1112,10 @@
         <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>4.8228797429133</v>
+        <v>4.84940842598802</v>
       </c>
       <c r="C7" s="1">
-        <v>2.91128496484833</v>
+        <v>2.97012251003535</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1115,10 +1123,10 @@
         <v>20</v>
       </c>
       <c r="B8" s="1">
-        <v>7.79636739815915</v>
+        <v>7.83429044730898</v>
       </c>
       <c r="C8" s="1">
-        <v>2.19263625022717</v>
+        <v>2.25058634178041</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1126,10 +1134,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="1">
-        <v>16.2575243960344</v>
+        <v>16.1833457560501</v>
       </c>
       <c r="C9" s="1">
-        <v>12.5325406536171</v>
+        <v>12.4220373220089</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1137,10 +1145,10 @@
         <v>30</v>
       </c>
       <c r="B10" s="1">
-        <v>39.1502108778063</v>
+        <v>39.285879980953</v>
       </c>
       <c r="C10" s="1">
-        <v>84.8793314679889</v>
+        <v>84.8310291018396</v>
       </c>
     </row>
   </sheetData>
